--- a/Excel Plug-In4/Fluid Capacity Mass.xlsx
+++ b/Excel Plug-In4/Fluid Capacity Mass.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gtvault-my.sharepoint.com/personal/lcalimlim3_gatech_edu/Documents/Documents/GitHub/ASE6002PEK/Excel Plug-In4/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3882" documentId="8_{272C6EFA-6A4D-4583-8144-6E15F1E4C899}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{73BF7769-75FB-45E1-933D-C4CB25FB4252}"/>
+  <xr:revisionPtr revIDLastSave="3980" documentId="8_{272C6EFA-6A4D-4583-8144-6E15F1E4C899}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C760EACE-3346-4389-A6EB-F3A75407CB33}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{46E85BB8-B567-4DDA-83E7-4BBB57F9E498}"/>
+    <workbookView xWindow="6345" yWindow="1125" windowWidth="21570" windowHeight="11295" xr2:uid="{46E85BB8-B567-4DDA-83E7-4BBB57F9E498}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -537,7 +537,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="2">
-        <f>(container_height*3.14*(container_diameter/2)*B5)/1000</f>
+        <f>UNC_Fluid_Fill*(container_height*3.14*(container_diameter/2)*B5)/1000</f>
         <v>0.23550000000000001</v>
       </c>
       <c r="C6" s="3" t="s">
@@ -549,7 +549,7 @@
         <v>8</v>
       </c>
       <c r="B7">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="C7" t="s">
         <v>9</v>

--- a/Excel Plug-In4/Fluid Capacity Mass.xlsx
+++ b/Excel Plug-In4/Fluid Capacity Mass.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07531a99d7244c5b/Documents/GitHub/ASE6002PEK/Excel Plug-In4/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14726" documentId="8_{272C6EFA-6A4D-4583-8144-6E15F1E4C899}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{59A1F6A1-386E-4696-962C-C83B60B1D2BD}"/>
+  <xr:revisionPtr revIDLastSave="35973" documentId="8_{272C6EFA-6A4D-4583-8144-6E15F1E4C899}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9A8A45F3-1507-42B3-AC6D-A40E3464C29E}"/>
   <bookViews>
     <workbookView xWindow="9105" yWindow="5325" windowWidth="38700" windowHeight="15345" xr2:uid="{46E85BB8-B567-4DDA-83E7-4BBB57F9E498}"/>
   </bookViews>
@@ -22,7 +22,7 @@
     <definedName name="fluid_mass">Sheet1!$B$6</definedName>
     <definedName name="UNC_Fluid_Fill">Sheet1!$B$7</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" calcMode="manual"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -504,7 +504,7 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>50.000450000000001</v>
+        <v>25</v>
       </c>
       <c r="C3" t="s">
         <v>2</v>
@@ -538,7 +538,7 @@
       </c>
       <c r="B6" s="2">
         <f>(container_height*3.14*(container_diameter/2)*B5)/1000</f>
-        <v>1.1775105975000002</v>
+        <v>0.58875</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>7</v>

--- a/Excel Plug-In4/Fluid Capacity Mass.xlsx
+++ b/Excel Plug-In4/Fluid Capacity Mass.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07531a99d7244c5b/Documents/GitHub/ASE6002PEK/Excel Plug-In4/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gtvault-my.sharepoint.com/personal/lcalimlim3_gatech_edu/Documents/Documents/GitHub/ASE6002PEK/Excel Plug-In4/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4322" documentId="8_{272C6EFA-6A4D-4583-8144-6E15F1E4C899}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{679164A8-4B94-42F0-B000-F8E1B48CB64E}"/>
+  <xr:revisionPtr revIDLastSave="4326" documentId="8_{272C6EFA-6A4D-4583-8144-6E15F1E4C899}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{80CF65DC-95BA-44CD-9238-2072475453F7}"/>
   <bookViews>
-    <workbookView xWindow="9105" yWindow="5325" windowWidth="38700" windowHeight="15345" xr2:uid="{46E85BB8-B567-4DDA-83E7-4BBB57F9E498}"/>
+    <workbookView xWindow="6795" yWindow="30" windowWidth="21570" windowHeight="11295" xr2:uid="{46E85BB8-B567-4DDA-83E7-4BBB57F9E498}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -500,7 +500,7 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>24.999980000000001</v>
+        <v>10</v>
       </c>
       <c r="C3" t="s">
         <v>2</v>
@@ -534,7 +534,7 @@
       </c>
       <c r="B6" s="2">
         <f>(container_height*3.14*(container_diameter/2)*B5)/1000</f>
-        <v>0.5887495290000001</v>
+        <v>0.23550000000000001</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>7</v>

--- a/Excel Plug-In4/Fluid Capacity Mass.xlsx
+++ b/Excel Plug-In4/Fluid Capacity Mass.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gtvault-my.sharepoint.com/personal/lcalimlim3_gatech_edu/Documents/Documents/GitHub/ASE6002PEK/Excel Plug-In4/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4326" documentId="8_{272C6EFA-6A4D-4583-8144-6E15F1E4C899}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{80CF65DC-95BA-44CD-9238-2072475453F7}"/>
+  <xr:revisionPtr revIDLastSave="4331" documentId="8_{272C6EFA-6A4D-4583-8144-6E15F1E4C899}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4DEB889B-8C6D-428A-ACBD-4EF035E815D0}"/>
   <bookViews>
-    <workbookView xWindow="6795" yWindow="30" windowWidth="21570" windowHeight="11295" xr2:uid="{46E85BB8-B567-4DDA-83E7-4BBB57F9E498}"/>
+    <workbookView xWindow="6255" yWindow="420" windowWidth="21570" windowHeight="11295" xr2:uid="{46E85BB8-B567-4DDA-83E7-4BBB57F9E498}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,6 @@
     <definedName name="container_height">Sheet1!$B$3</definedName>
     <definedName name="fluid_density">Sheet1!$B$5</definedName>
     <definedName name="fluid_mass">Sheet1!$B$6</definedName>
-    <definedName name="UNC_Fluid_Fill">Sheet1!$B$7</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="8">
   <si>
     <t>Fluid Capacity</t>
   </si>
@@ -67,12 +66,6 @@
   </si>
   <si>
     <t>kg</t>
-  </si>
-  <si>
-    <t>UNC_Fluid_Fill</t>
-  </si>
-  <si>
-    <t>% fluid fill</t>
   </si>
 </sst>
 </file>
@@ -165,6 +158,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -484,7 +481,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEFDEF44-065B-42CA-93FA-BEEED9D4D5AA}">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.28515625" customWidth="1"/>
@@ -540,17 +537,6 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7">
-        <v>0.8</v>
-      </c>
-      <c r="C7" t="s">
-        <v>9</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Excel Plug-In4/Fluid Capacity Mass.xlsx
+++ b/Excel Plug-In4/Fluid Capacity Mass.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gtvault-my.sharepoint.com/personal/lcalimlim3_gatech_edu/Documents/Documents/GitHub/ASE6002PEK/Excel Plug-In4/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07531a99d7244c5b/Documents/GitHub/ASE6002PEK/Excel Plug-In4/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4331" documentId="8_{272C6EFA-6A4D-4583-8144-6E15F1E4C899}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4DEB889B-8C6D-428A-ACBD-4EF035E815D0}"/>
+  <xr:revisionPtr revIDLastSave="5577" documentId="121_{8A5171F7-E627-4791-9770-5DDCB9860D0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{516A0A1D-6F09-45D5-9A1C-2C1481A5EAEB}"/>
   <bookViews>
-    <workbookView xWindow="6255" yWindow="420" windowWidth="21570" windowHeight="11295" xr2:uid="{46E85BB8-B567-4DDA-83E7-4BBB57F9E498}"/>
+    <workbookView xWindow="9105" yWindow="5325" windowWidth="38700" windowHeight="15345" xr2:uid="{46E85BB8-B567-4DDA-83E7-4BBB57F9E498}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
     <definedName name="fluid_density">Sheet1!$B$5</definedName>
     <definedName name="fluid_mass">Sheet1!$B$6</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" calcMode="manual"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>

--- a/Excel Plug-In4/Fluid Capacity Mass.xlsx
+++ b/Excel Plug-In4/Fluid Capacity Mass.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07531a99d7244c5b/Documents/GitHub/ASE6002PEK/Excel Plug-In4/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5577" documentId="121_{8A5171F7-E627-4791-9770-5DDCB9860D0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{516A0A1D-6F09-45D5-9A1C-2C1481A5EAEB}"/>
+  <xr:revisionPtr revIDLastSave="5583" documentId="121_{8A5171F7-E627-4791-9770-5DDCB9860D0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B217B7A9-22FA-4FB7-84ED-62803C786667}"/>
   <bookViews>
     <workbookView xWindow="9105" yWindow="5325" windowWidth="38700" windowHeight="15345" xr2:uid="{46E85BB8-B567-4DDA-83E7-4BBB57F9E498}"/>
   </bookViews>

--- a/Excel Plug-In4/Fluid Capacity Mass.xlsx
+++ b/Excel Plug-In4/Fluid Capacity Mass.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07531a99d7244c5b/Documents/GitHub/ASE6002PEK/Excel Plug-In4/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5583" documentId="121_{8A5171F7-E627-4791-9770-5DDCB9860D0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B217B7A9-22FA-4FB7-84ED-62803C786667}"/>
+  <xr:revisionPtr revIDLastSave="5586" documentId="121_{8A5171F7-E627-4791-9770-5DDCB9860D0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E59DAC1F-80D4-480A-84EE-5BCC2EBCE432}"/>
   <bookViews>
     <workbookView xWindow="9105" yWindow="5325" windowWidth="38700" windowHeight="15345" xr2:uid="{46E85BB8-B567-4DDA-83E7-4BBB57F9E498}"/>
   </bookViews>

--- a/Excel Plug-In4/Fluid Capacity Mass.xlsx
+++ b/Excel Plug-In4/Fluid Capacity Mass.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07531a99d7244c5b/Documents/GitHub/ASE6002PEK/Excel Plug-In4/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5586" documentId="121_{8A5171F7-E627-4791-9770-5DDCB9860D0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E59DAC1F-80D4-480A-84EE-5BCC2EBCE432}"/>
+  <xr:revisionPtr revIDLastSave="5589" documentId="121_{8A5171F7-E627-4791-9770-5DDCB9860D0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A9F71360-AF27-4A0D-9F41-8D76B296B290}"/>
   <bookViews>
     <workbookView xWindow="9105" yWindow="5325" windowWidth="38700" windowHeight="15345" xr2:uid="{46E85BB8-B567-4DDA-83E7-4BBB57F9E498}"/>
   </bookViews>

--- a/Excel Plug-In4/Fluid Capacity Mass.xlsx
+++ b/Excel Plug-In4/Fluid Capacity Mass.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07531a99d7244c5b/Documents/GitHub/ASE6002PEK/Excel Plug-In4/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5589" documentId="121_{8A5171F7-E627-4791-9770-5DDCB9860D0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A9F71360-AF27-4A0D-9F41-8D76B296B290}"/>
+  <xr:revisionPtr revIDLastSave="5592" documentId="121_{8A5171F7-E627-4791-9770-5DDCB9860D0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{101EF77B-D1F3-4B8E-A741-C1D8966D7A80}"/>
   <bookViews>
     <workbookView xWindow="9105" yWindow="5325" windowWidth="38700" windowHeight="15345" xr2:uid="{46E85BB8-B567-4DDA-83E7-4BBB57F9E498}"/>
   </bookViews>
